--- a/database/student.xlsx
+++ b/database/student.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,86 +413,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Login Email</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Full Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Staff ID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Department</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Designation</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Joining Date</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Personal Email</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Base Salary/Fee</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Paid/HRA</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Workshop Status</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Payment Status</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Pan Number</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Bank Account</t>
         </is>
@@ -564,7 +552,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -642,7 +630,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -720,12 +708,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Ongoing</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1172,12 +1160,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>+977 9763606459</t>
+          <t>+977 9700012009</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>prayudgurung@gmail.com</t>
+          <t>prayudgurung13@gmail.com</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1250,12 +1238,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>+977 9860339637</t>
+          <t>+977 9824311171</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>arbin@gmail.com</t>
+          <t>arbinch345@gmail.com</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1363,6 +1351,396 @@
         </is>
       </c>
       <c r="P12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>student@ems.com</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Generic Student</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>STD-001</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>std-marketing-sujata@ems.com</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Sujata Shrestha</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ST-MKT-002</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Digital Marketing</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>+977 9702518447</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>shersujata7@gmail.com</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>15000</v>
+      </c>
+      <c r="K14" t="n">
+        <v>15000</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Fully Paid</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>std-it-sakshyam@ems.com</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sakshyam Pudasaini</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ST-IT-011</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Cyber Security</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>+977 9767969372</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>pudasainisakshyam@gmail.com</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Unpaid</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>std-it-jenesis@ems.com</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Jenesis Maharjan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ST-IT-012</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>AI/ML</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>+977 9745346660</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>jenesismaharjan@gmail.com</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>16000</v>
+      </c>
+      <c r="K16" t="n">
+        <v>16000</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Fully Paid</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>std-it-shirish@ems.com</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Shirish Tha Shrestha</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ST-IT-013</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Al/ML</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>+977 9840256503</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>shresthashirish14@gmail.com</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>15000</v>
+      </c>
+      <c r="K17" t="n">
+        <v>15000</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Fully Paid</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>

--- a/database/student.xlsx
+++ b/database/student.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,86 +425,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Login Email</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Full Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Staff ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Department</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Designation</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Joining Date</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Personal Email</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Base Salary/Fee</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Paid/HRA</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Workshop Status</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Payment Status</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Pan Number</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Bank Account</t>
         </is>
@@ -552,7 +564,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -630,7 +642,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -708,12 +720,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Inactive</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Ongoing</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1160,12 +1172,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>+977 9700012009</t>
+          <t>+977 9763606459</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>prayudgurung13@gmail.com</t>
+          <t>prayudgurung@gmail.com</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1238,12 +1250,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>+977 9824311171</t>
+          <t>+977 9860339637</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>arbinch345@gmail.com</t>
+          <t>arbin@gmail.com</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1351,396 +1363,6 @@
         </is>
       </c>
       <c r="P12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>student@ems.com</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Generic Student</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>STD-001</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Student</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Student</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2023-01-01</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>50000</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Ongoing</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>std-marketing-sujata@ems.com</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Sujata Shrestha</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>ST-MKT-002</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Student</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Digital Marketing</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>+977 9702518447</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>shersujata7@gmail.com</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>15000</v>
-      </c>
-      <c r="K14" t="n">
-        <v>15000</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Ongoing</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Fully Paid</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>std-it-sakshyam@ems.com</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Sakshyam Pudasaini</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>ST-IT-011</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Student</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Cyber Security</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>+977 9767969372</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>pudasainisakshyam@gmail.com</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Ongoing</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Unpaid</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>std-it-jenesis@ems.com</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Jenesis Maharjan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>ST-IT-012</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Student</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>AI/ML</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>+977 9745346660</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>jenesismaharjan@gmail.com</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>16000</v>
-      </c>
-      <c r="K16" t="n">
-        <v>16000</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Ongoing</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Fully Paid</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>std-it-shirish@ems.com</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Shirish Tha Shrestha</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>ST-IT-013</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Student</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Al/ML</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>+977 9840256503</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>shresthashirish14@gmail.com</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>15000</v>
-      </c>
-      <c r="K17" t="n">
-        <v>15000</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Ongoing</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Fully Paid</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
